--- a/reports/devops-juniors-israel-2026-W25.xlsx
+++ b/reports/devops-juniors-israel-2026-W25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="375">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-15T12:39:24</t>
+    <t xml:space="preserve">2026-06-16T11:31:36</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -166,6 +166,24 @@
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
+    <t xml:space="preserve">HPC &amp; Linux Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-linux-systems-engineer-at-ben-gurion-university-of-the-negev-4427607653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">Technical Support Engineer</t>
   </si>
   <si>
@@ -220,6 +238,18 @@
     <t xml:space="preserve">2026-06-01</t>
   </si>
   <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4408743594</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
@@ -232,382 +262,379 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
   </si>
   <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer – Microsoft Infrastructure &amp; Cloud (Help Desk + 3rd Tier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G-MEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-%E2%80%93-microsoft-infrastructure-cloud-help-desk-%2B-3rd-tier-at-g-mel-4429114041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (36613)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-36613-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428823042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machine Learning Student, (MSc Students)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edwards Lifesciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/machine-learning-student-msc-students-at-edwards-lifesciences-4423656161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-at-nebius-4425236974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux Software Embedded Engineer (Junior position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDA Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-software-embedded-engineer-junior-position-at-mda-space-4422723139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
   </si>
   <si>
     <t xml:space="preserve">Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4423356724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Candex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-candex-4410031859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-administrator-at-check-point-software-4425741384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machine Learning Student, (MSc Students)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edwards Lifesciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/machine-learning-student-msc-students-at-edwards-lifesciences-4423656161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-at-nebius-4425236974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk &amp; IT Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-it-administrator-at-mize-4425999700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux Software Embedded Engineer (Junior position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDA Space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-software-embedded-engineer-junior-position-at-mda-space-4422723139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategy Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
   </si>
   <si>
     <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
@@ -631,7 +658,22 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-25</t>
+    <t xml:space="preserve">IT Support Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plarium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-administrator-at-plarium-4402847792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-extreme-4426743545</t>
   </si>
   <si>
     <t xml:space="preserve">טכנאי/ת Help Desk</t>
@@ -643,199 +685,217 @@
     <t xml:space="preserve">Ashdod, South District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell, Active Directory</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-extreme-4426743545</t>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algorithm System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/algorithm-system-engineer-at-elbit-systems-israel-4412906510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">דרוש/ה Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELPC - IT &amp; SECURITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%93%D7%A8%D7%95%D7%A9-%D7%94-help-desk-technician-at-elpc-it-security-4429264653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassesUSA.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4400413150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4425818718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk - 239819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
   </si>
   <si>
     <t xml:space="preserve">Technical Support Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Intezer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk tier 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accel Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-tier-2-at-accel-solutions-4425769508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4422293340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk - 239819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
   </si>
   <si>
     <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
@@ -850,18 +910,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragontail Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4422278367</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zoho</t>
   </si>
   <si>
@@ -871,21 +919,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Representative (Full-Time, On-Site | Be’er Sheva – Gav Yam Park)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SITE123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-representative-full-time-on-site-be%E2%80%99er-sheva-%E2%80%93-gav-yam-park-at-site123-4419228442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Operations Specialist</t>
   </si>
   <si>
@@ -946,114 +979,105 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
+    <t xml:space="preserve">Service Desk Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician (34817)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-34817-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428805862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Especialista de Soporte Service Desk Remoto Horario rotativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lima, Lima, PerÃº</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-especialista-de-soporte-service-desk-remoto-horario-rotativo-canvia-1133349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Success Advisor Evenings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walden University</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columbia, Columbia, Maryland, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-advisor-evenings-walden-university-1133418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-at-comblack-4427544458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4425470752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Support &amp; Systems Operations Specialist- position no. 1601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBI Investment House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-support-systems-operations-specialist-position-no-1601-at-ibi-investment-house-4423609880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Especialista de Soporte Service Desk Remoto Horario rotativo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canvia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lima, Lima, PerÃº</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-especialista-de-soporte-service-desk-remoto-horario-rotativo-canvia-1133349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Advisor Evenings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walden University</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columbia, Columbia, Maryland, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-advisor-evenings-walden-university-1133418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
@@ -1072,16 +1096,16 @@
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1239,7 +1263,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -1247,7 +1271,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1255,7 +1279,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -1263,7 +1287,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -1345,7 +1369,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
@@ -1353,7 +1377,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1361,7 +1385,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1395,7 +1419,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29">
@@ -1423,7 +1447,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1511,10 +1535,10 @@
         <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>53</v>
@@ -1543,10 +1567,10 @@
         <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>59</v>
@@ -1575,10 +1599,10 @@
         <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>65</v>
@@ -1604,25 +1628,25 @@
         <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -1630,31 +1654,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
@@ -1668,25 +1692,25 @@
         <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="3">
+        <v>57</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3">
-        <v>52</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -1694,31 +1718,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="3">
+        <v>52</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="3">
-        <v>51</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -1726,13 +1750,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
@@ -1741,13 +1765,13 @@
         <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>49</v>
@@ -1758,31 +1782,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -1790,31 +1814,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -1822,31 +1846,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F13" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14">
@@ -1854,31 +1878,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1886,13 +1910,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
@@ -1901,16 +1925,16 @@
         <v>32</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16">
@@ -1918,31 +1942,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
@@ -1950,13 +1974,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
@@ -1965,16 +1989,16 @@
         <v>30</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -1982,13 +2006,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
@@ -1997,16 +2021,16 @@
         <v>30</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19">
@@ -2014,13 +2038,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>26</v>
@@ -2029,16 +2053,16 @@
         <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20">
@@ -2046,31 +2070,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21">
@@ -2078,13 +2102,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -2093,16 +2117,16 @@
         <v>27</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22">
@@ -2110,13 +2134,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
@@ -2125,16 +2149,16 @@
         <v>26</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23">
@@ -2142,13 +2166,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -2157,13 +2181,13 @@
         <v>26</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>49</v>
@@ -2174,13 +2198,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="D24" s="3" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>26</v>
@@ -2189,13 +2213,13 @@
         <v>24</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>49</v>
@@ -2206,13 +2230,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
@@ -2221,16 +2245,16 @@
         <v>23</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26">
@@ -2238,13 +2262,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
@@ -2253,13 +2277,13 @@
         <v>20</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>49</v>
@@ -2315,7 +2339,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -2330,22 +2354,22 @@
         <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2">
@@ -2368,7 +2392,7 @@
         <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2380,7 +2404,7 @@
         <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -2394,16 +2418,16 @@
         <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" s="3">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2415,7 +2439,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2429,16 +2453,16 @@
         <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2450,7 +2474,7 @@
         <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -2464,16 +2488,16 @@
         <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2485,7 +2509,7 @@
         <v>67</v>
       </c>
       <c r="K5" s="3">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2496,66 +2520,66 @@
         <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="K6" s="3">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="K7" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2566,77 +2590,77 @@
         <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="3">
+        <v>57</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="3">
-        <v>52</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="K8" s="3">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="3">
+        <v>52</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="3">
-        <v>51</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="K9" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
@@ -2645,54 +2669,54 @@
         <v>47</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>49</v>
       </c>
       <c r="K10" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="K11" s="3">
         <v>14</v>
@@ -2700,118 +2724,118 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K12" s="3">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="K14" s="3">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
@@ -2820,68 +2844,68 @@
         <v>32</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K15" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K16" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
@@ -2890,33 +2914,33 @@
         <v>30</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K17" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
@@ -2925,33 +2949,33 @@
         <v>30</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>26</v>
@@ -2960,68 +2984,68 @@
         <v>28</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="K19" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="K20" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
@@ -3030,33 +3054,33 @@
         <v>27</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="K21" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>27</v>
@@ -3065,33 +3089,33 @@
         <v>26</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>27</v>
@@ -3100,33 +3124,33 @@
         <v>26</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>49</v>
       </c>
       <c r="K23" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="C24" s="3" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>26</v>
@@ -3135,33 +3159,33 @@
         <v>24</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>49</v>
       </c>
       <c r="K24" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
@@ -3170,33 +3194,33 @@
         <v>23</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K25" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
@@ -3205,33 +3229,33 @@
         <v>20</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>49</v>
       </c>
       <c r="K26" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
@@ -3240,138 +3264,138 @@
         <v>20</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>100</v>
+        <v>181</v>
       </c>
       <c r="K27" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>64</v>
+        <v>184</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E28" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="K28" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E29" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="K29" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K30" s="3">
         <v>32</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="K30" s="3">
-        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>27</v>
@@ -3380,33 +3404,33 @@
         <v>13</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="K31" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>74</v>
+        <v>204</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>27</v>
@@ -3415,68 +3439,68 @@
         <v>13</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K32" s="3">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>80</v>
+        <v>204</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E33" s="3">
         <v>13</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="K33" s="3">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3485,33 +3509,33 @@
         <v>13</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>61</v>
+        <v>206</v>
       </c>
       <c r="K34" s="3">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>132</v>
+        <v>215</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
@@ -3520,33 +3544,33 @@
         <v>13</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="K35" s="3">
-        <v>4</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>213</v>
+        <v>137</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
@@ -3555,138 +3579,138 @@
         <v>13</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>136</v>
+        <v>67</v>
       </c>
       <c r="K36" s="3">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="3">
+        <v>13</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" s="3">
-        <v>10</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="G37" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="K37" s="3">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>50</v>
+        <v>194</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="K38" s="3">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E39" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>130</v>
+        <v>202</v>
       </c>
       <c r="K39" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3695,30 +3719,30 @@
         <v>10</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>130</v>
+        <v>202</v>
       </c>
       <c r="K40" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>231</v>
+        <v>56</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>233</v>
@@ -3730,45 +3754,45 @@
         <v>10</v>
       </c>
       <c r="F41" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>235</v>
-      </c>
       <c r="J41" s="3" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="K41" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>110</v>
+        <v>235</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="D42" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>238</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
@@ -3777,10 +3801,10 @@
         <v>239</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="K42" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -3791,159 +3815,159 @@
         <v>241</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="3">
+        <v>10</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E43" s="3">
-        <v>8</v>
-      </c>
-      <c r="F43" s="3" t="s">
+      <c r="G43" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="J43" s="3" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="K43" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="C44" s="3" t="s">
-        <v>133</v>
+        <v>246</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>200</v>
+        <v>249</v>
       </c>
       <c r="K44" s="3">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>250</v>
+        <v>70</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="K45" s="3">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>57</v>
+        <v>255</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>161</v>
+        <v>55</v>
       </c>
       <c r="K46" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>256</v>
+        <v>118</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>258</v>
+        <v>120</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E47" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>259</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
@@ -3952,33 +3976,33 @@
         <v>260</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>261</v>
+        <v>153</v>
       </c>
       <c r="K47" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="D48" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E48" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>264</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
@@ -3987,10 +4011,10 @@
         <v>265</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>130</v>
+        <v>202</v>
       </c>
       <c r="K48" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49">
@@ -3998,10 +4022,10 @@
         <v>266</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>267</v>
+        <v>155</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
@@ -4010,10 +4034,10 @@
         <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
@@ -4022,21 +4046,21 @@
         <v>268</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="K49" s="3">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>201</v>
+        <v>269</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
@@ -4045,33 +4069,33 @@
         <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="K50" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>272</v>
+        <v>63</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>97</v>
+        <v>274</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
@@ -4080,33 +4104,33 @@
         <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="K51" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4115,33 +4139,33 @@
         <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>246</v>
+        <v>279</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>77</v>
+        <v>281</v>
       </c>
       <c r="K52" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4150,33 +4174,33 @@
         <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="K53" s="3">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>108</v>
+        <v>287</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4185,33 +4209,33 @@
         <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>105</v>
+        <v>202</v>
       </c>
       <c r="K54" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>287</v>
+        <v>110</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4220,138 +4244,138 @@
         <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>243</v>
+        <v>284</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>289</v>
+        <v>135</v>
       </c>
       <c r="K55" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>291</v>
+        <v>155</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>292</v>
+        <v>115</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I56" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>294</v>
-      </c>
       <c r="J56" s="3" t="s">
-        <v>236</v>
+        <v>87</v>
       </c>
       <c r="K56" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="D57" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I57" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>298</v>
-      </c>
       <c r="J57" s="3" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="K57" s="3">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E58" s="3">
+        <v>6</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="G58" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E58" s="3">
-        <v>4</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>302</v>
-      </c>
       <c r="J58" s="3" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="K58" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>26</v>
@@ -4360,138 +4384,138 @@
         <v>4</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>61</v>
+        <v>249</v>
       </c>
       <c r="K59" s="3">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>44</v>
+        <v>306</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>292</v>
+        <v>104</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E60" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="K60" s="3">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E61" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="K61" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E62" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="K62" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>97</v>
+        <v>303</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
@@ -4500,33 +4524,33 @@
         <v>3</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="K63" s="3">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>50</v>
+        <v>317</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>25</v>
@@ -4535,19 +4559,19 @@
         <v>3</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="K64" s="3">
         <v>22</v>
@@ -4555,13 +4579,13 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>108</v>
+        <v>323</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>25</v>
@@ -4570,33 +4594,33 @@
         <v>3</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="K65" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>322</v>
+        <v>114</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>323</v>
+        <v>115</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>25</v>
@@ -4605,59 +4629,127 @@
         <v>3</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K66" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E67" s="3">
-        <v>0</v>
-      </c>
-      <c r="F67" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>319</v>
+      </c>
       <c r="G67" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="K67" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E68" s="3">
         <v>0</v>
       </c>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K68" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E69" s="3">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K69" s="3">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K67"/>
+  <autoFilter ref="A1:K69"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4725,6 +4817,8 @@
     <hyperlink ref="I65" r:id="rId64"/>
     <hyperlink ref="I66" r:id="rId65"/>
     <hyperlink ref="I67" r:id="rId66"/>
+    <hyperlink ref="I68" r:id="rId67"/>
+    <hyperlink ref="I69" r:id="rId68"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4732,9 +4826,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4755,10 +4849,10 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>43</v>
@@ -4766,79 +4860,79 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>223</v>
+        <v>140</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>224</v>
+        <v>141</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>225</v>
+        <v>142</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>226</v>
+        <v>143</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
@@ -4847,84 +4941,63 @@
         <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>110</v>
+        <v>321</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>237</v>
+        <v>322</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>238</v>
+        <v>304</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>239</v>
+        <v>324</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>262</v>
+        <v>325</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>263</v>
+        <v>114</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>264</v>
+        <v>304</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>265</v>
+        <v>326</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G7"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -4932,7 +5005,6 @@
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
     <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4947,178 +5019,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B2" s="3">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="B4" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B6" s="3">
         <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>339</v>
+        <v>200</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>297</v>
+        <v>348</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>196</v>
+        <v>308</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>312</v>
+        <v>242</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B12" s="3">
         <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -5138,10 +5210,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
@@ -5149,10 +5221,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3">
@@ -5160,10 +5232,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4">
@@ -5171,10 +5243,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5">
@@ -5185,7 +5257,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6">
@@ -5196,7 +5268,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -5217,13 +5289,13 @@
         <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2">
@@ -5234,7 +5306,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5243,10 +5315,10 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -5258,7 +5330,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W25.xlsx
+++ b/reports/devops-juniors-israel-2026-W25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="406">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-16T11:31:36</t>
+    <t xml:space="preserve">2026-06-17T11:15:19</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -166,7 +166,463 @@
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
-    <t xml:space="preserve">HPC &amp; Linux Systems Engineer</t>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-ai-4427315937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (36613)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-36613-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428823042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-administrator-at-check-point-software-4427626178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAREL LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux Software Embedded Engineer (Junior position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDA Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-software-embedded-engineer-junior-position-at-mda-space-4422723139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer Systems Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Ben-Gurion University of the Negev</t>
@@ -175,870 +631,513 @@
     <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-linux-systems-engineer-at-ben-gurion-university-of-the-negev-4427607653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT / Cloud Specialist - 235226</t>
+    <t xml:space="preserve">Git, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-systems-engineer-at-ben-gurion-university-of-the-negev-4428645689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plarium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-administrator-at-plarium-4402847792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intezer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-sela-4426498040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassesUSA.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4400413150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpotNet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spotnet-4426875292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accel Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-accel-solutions-4427341027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4425818718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk - 239819</t>
   </si>
   <si>
     <t xml:space="preserve">Experis Israel</t>
   </si>
   <si>
+    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragontail Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4422278367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Representative (Full-Time, On-Site | Be’er Sheva – Gav Yam Park)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SITE123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-representative-full-time-on-site-be%E2%80%99er-sheva-%E2%80%93-gav-yam-park-at-site123-4419228442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innocom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-innocom-4427324663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4423614421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4419979615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician (34817)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-34817-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428805862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Haifa, Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-cloud-specialist-235226-at-experis-israel-4423620429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4408743594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer – Microsoft Infrastructure &amp; Cloud (Help Desk + 3rd Tier)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-MEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-%E2%80%93-microsoft-infrastructure-cloud-help-desk-%2B-3rd-tier-at-g-mel-4429114041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (36613)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-36613-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428823042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machine Learning Student, (MSc Students)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edwards Lifesciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/machine-learning-student-msc-students-at-edwards-lifesciences-4423656161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-at-nebius-4425236974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux Software Embedded Engineer (Junior position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDA Space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-software-embedded-engineer-junior-position-at-mda-space-4422723139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategy Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plarium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-administrator-at-plarium-4402847792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-extreme-4426743545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Algorithm System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/algorithm-system-engineer-at-elbit-systems-israel-4412906510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">דרוש/ה Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELPC - IT &amp; SECURITY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%93%D7%A8%D7%95%D7%A9-%D7%94-help-desk-technician-at-elpc-it-security-4429264653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GlassesUSA.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4400413150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4425818718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk - 239819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excis Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4425470752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Support &amp; Systems Operations Specialist- position no. 1601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-support-systems-operations-specialist-position-no-1601-at-ibi-investment-house-4423609880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-south-apac-sea-anz-ind-subcont-4390170199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unframe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-unframe-4425465742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-4417759260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Become a Student Life Coach Flexible Role UK Â£20 Â£40 hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-become-a-student-life-coach-flexible-role-uk-20-40-hr-findtutors-1133462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Success Advisor Evenings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walden University</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columbia, Columbia, Maryland, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-advisor-evenings-walden-university-1133418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4423670353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4423614421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician (34817)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-34817-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428805862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Especialista de Soporte Service Desk Remoto Horario rotativo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canvia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lima, Lima, PerÃº</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-especialista-de-soporte-service-desk-remoto-horario-rotativo-canvia-1133349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Advisor Evenings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walden University</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columbia, Columbia, Maryland, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-advisor-evenings-walden-university-1133418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
@@ -1048,16 +1147,22 @@
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
@@ -1066,21 +1171,9 @@
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
@@ -1090,6 +1183,12 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
@@ -1100,12 +1199,6 @@
   </si>
   <si>
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1263,7 +1356,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7">
@@ -1271,7 +1364,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1279,7 +1372,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -1287,7 +1380,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10">
@@ -1369,7 +1462,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
@@ -1377,7 +1470,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -1385,7 +1478,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1419,7 +1512,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29">
@@ -1427,7 +1520,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -1447,7 +1540,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1535,10 +1628,10 @@
         <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>53</v>
@@ -1567,10 +1660,10 @@
         <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>59</v>
@@ -1596,25 +1689,25 @@
         <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="3">
+        <v>74</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="3">
-        <v>83</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -1622,31 +1715,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="3">
+        <v>57</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="3">
-        <v>74</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -1654,31 +1747,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3">
+        <v>52</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3">
-        <v>61</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="8">
@@ -1686,31 +1779,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="3">
+        <v>52</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="3">
-        <v>57</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -1718,31 +1811,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="3">
+        <v>47</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="3">
-        <v>52</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -1750,13 +1843,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
@@ -1765,13 +1858,13 @@
         <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>49</v>
@@ -1782,13 +1875,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>25</v>
@@ -1797,16 +1890,16 @@
         <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12">
@@ -1814,31 +1907,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -1846,31 +1939,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="3">
+        <v>44</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="3">
-        <v>37</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -1878,31 +1971,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15">
@@ -1910,31 +2003,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3">
+        <v>40</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="3">
-        <v>32</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="16">
@@ -1942,13 +2035,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>26</v>
@@ -1957,16 +2050,16 @@
         <v>32</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17">
@@ -1974,31 +2067,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="3">
+        <v>32</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="3">
-        <v>30</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -2006,31 +2099,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="3">
+        <v>32</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="3">
-        <v>30</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="19">
@@ -2038,31 +2131,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>137</v>
+        <v>45</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20">
@@ -2070,31 +2163,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>58</v>
+        <v>136</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21">
@@ -2102,31 +2195,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3">
+        <v>30</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="3">
-        <v>27</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="22">
@@ -2134,31 +2227,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="3">
+        <v>30</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="3">
-        <v>26</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
@@ -2166,31 +2259,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="3">
         <v>27</v>
       </c>
-      <c r="F23" s="3">
-        <v>26</v>
-      </c>
       <c r="G23" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24">
@@ -2198,31 +2291,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>155</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25">
@@ -2230,31 +2323,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="3">
+        <v>26</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="3">
-        <v>23</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>164</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26">
@@ -2262,28 +2355,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>49</v>
@@ -2326,7 +2419,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2339,7 +2432,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -2354,22 +2447,22 @@
         <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2">
@@ -2392,7 +2485,7 @@
         <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2404,7 +2497,7 @@
         <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -2418,16 +2511,16 @@
         <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2439,7 +2532,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -2453,16 +2546,16 @@
         <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2474,7 +2567,7 @@
         <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -2485,182 +2578,182 @@
         <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3">
+        <v>74</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="3">
-        <v>83</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="K5" s="3">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="3">
+        <v>57</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="3">
-        <v>74</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="K6" s="3">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="3">
+        <v>52</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3">
-        <v>61</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="K7" s="3">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="3">
+        <v>52</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="3">
-        <v>57</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="K8" s="3">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="3">
+        <v>47</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="3">
-        <v>52</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="K9" s="3">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
@@ -2669,33 +2762,33 @@
         <v>47</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>49</v>
       </c>
       <c r="K10" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>25</v>
@@ -2704,173 +2797,173 @@
         <v>44</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="K11" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K12" s="3">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="3">
+        <v>44</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="3">
-        <v>37</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="K13" s="3">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="K14" s="3">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="3">
+        <v>40</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="3">
-        <v>32</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>26</v>
@@ -2879,733 +2972,733 @@
         <v>32</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K16" s="3">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="3">
+        <v>32</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="3">
-        <v>30</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="K17" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="3">
+        <v>32</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="3">
-        <v>30</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="K18" s="3">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>137</v>
+        <v>45</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="K19" s="3">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>58</v>
+        <v>136</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>30</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3">
-        <v>27</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="K21" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="3">
+        <v>30</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="3">
-        <v>26</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="K22" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="3">
         <v>27</v>
       </c>
-      <c r="E23" s="3">
-        <v>26</v>
-      </c>
       <c r="F23" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="K23" s="3">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>155</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="K24" s="3">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="3">
+        <v>26</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="3">
-        <v>23</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>164</v>
+        <v>49</v>
       </c>
       <c r="K25" s="3">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>49</v>
       </c>
       <c r="K26" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="K27" s="3">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>187</v>
+        <v>49</v>
       </c>
       <c r="K28" s="3">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>193</v>
+        <v>81</v>
       </c>
       <c r="K29" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>194</v>
+        <v>62</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>184</v>
+        <v>58</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>49</v>
       </c>
       <c r="K30" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E31" s="3">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="K31" s="3">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E32" s="3">
+        <v>17</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="K32" s="3">
         <v>13</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="K32" s="3">
-        <v>22</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>207</v>
+        <v>56</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>199</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>200</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>209</v>
+        <v>49</v>
       </c>
       <c r="K33" s="3">
-        <v>8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E34" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="K34" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>84</v>
+        <v>209</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E35" s="3">
         <v>13</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>49</v>
+        <v>212</v>
       </c>
       <c r="K35" s="3">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>58</v>
+        <v>209</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E36" s="3">
         <v>13</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>67</v>
+        <v>215</v>
       </c>
       <c r="K36" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>222</v>
+        <v>52</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
@@ -3617,100 +3710,100 @@
         <v>218</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>67</v>
+        <v>212</v>
       </c>
       <c r="K37" s="3">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="3">
+        <v>13</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" s="3">
-        <v>12</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="G38" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="K38" s="3">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>204</v>
+        <v>101</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>200</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>202</v>
+        <v>108</v>
       </c>
       <c r="K39" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>230</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3719,30 +3812,30 @@
         <v>10</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="J40" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="K40" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>233</v>
@@ -3754,10 +3847,10 @@
         <v>10</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>32</v>
@@ -3766,21 +3859,21 @@
         <v>234</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="K41" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>236</v>
-      </c>
       <c r="C42" s="3" t="s">
-        <v>237</v>
+        <v>122</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
@@ -3789,33 +3882,33 @@
         <v>10</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="K42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
@@ -3824,22 +3917,22 @@
         <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I43" s="3" t="s">
+      <c r="J43" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="K43" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
@@ -3850,7 +3943,7 @@
         <v>245</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>246</v>
+        <v>58</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3859,33 +3952,33 @@
         <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>248</v>
-      </c>
       <c r="J44" s="3" t="s">
-        <v>249</v>
+        <v>212</v>
       </c>
       <c r="K44" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>250</v>
+        <v>139</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>70</v>
+        <v>249</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3894,33 +3987,33 @@
         <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="K45" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>254</v>
+        <v>62</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>256</v>
+        <v>58</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
@@ -3929,208 +4022,208 @@
         <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>55</v>
+        <v>232</v>
       </c>
       <c r="K46" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>118</v>
+        <v>254</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="3">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="J47" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E47" s="3">
-        <v>8</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="K47" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" s="3">
+        <v>10</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E48" s="3">
-        <v>8</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>265</v>
-      </c>
       <c r="J48" s="3" t="s">
-        <v>202</v>
+        <v>81</v>
       </c>
       <c r="K48" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>155</v>
+        <v>263</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>115</v>
+        <v>264</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>267</v>
+        <v>230</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>209</v>
+        <v>98</v>
       </c>
       <c r="K49" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>269</v>
+        <v>126</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E50" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>153</v>
+        <v>258</v>
       </c>
       <c r="K50" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E51" s="3">
+        <v>8</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E51" s="3">
-        <v>6</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>275</v>
-      </c>
       <c r="J51" s="3" t="s">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="K51" s="3">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>277</v>
+        <v>159</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>278</v>
+        <v>122</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4139,33 +4232,33 @@
         <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>281</v>
+        <v>215</v>
       </c>
       <c r="K52" s="3">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4174,33 +4267,33 @@
         <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>206</v>
+        <v>258</v>
       </c>
       <c r="K53" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>210</v>
+        <v>281</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4209,33 +4302,33 @@
         <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="K54" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>110</v>
+        <v>287</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4244,33 +4337,33 @@
         <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>135</v>
+        <v>290</v>
       </c>
       <c r="K55" s="3">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="C56" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4279,33 +4372,33 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="K56" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>296</v>
+        <v>58</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
@@ -4314,10 +4407,10 @@
         <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>31</v>
@@ -4326,7 +4419,7 @@
         <v>297</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="K57" s="3">
         <v>23</v>
@@ -4334,13 +4427,13 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>298</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
@@ -4352,7 +4445,7 @@
         <v>299</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>31</v>
@@ -4361,10 +4454,10 @@
         <v>300</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="K58" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -4375,28 +4468,28 @@
         <v>302</v>
       </c>
       <c r="C59" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" s="3">
+        <v>6</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E59" s="3">
-        <v>4</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>305</v>
-      </c>
       <c r="J59" s="3" t="s">
-        <v>249</v>
+        <v>113</v>
       </c>
       <c r="K59" s="3">
         <v>19</v>
@@ -4404,34 +4497,34 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6</v>
+      </c>
+      <c r="F60" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="G60" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I60" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E60" s="3">
-        <v>4</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>309</v>
-      </c>
       <c r="J60" s="3" t="s">
-        <v>129</v>
+        <v>192</v>
       </c>
       <c r="K60" s="3">
         <v>7</v>
@@ -4439,142 +4532,142 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I61" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E61" s="3">
-        <v>4</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>313</v>
-      </c>
       <c r="J61" s="3" t="s">
-        <v>181</v>
+        <v>55</v>
       </c>
       <c r="K61" s="3">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>301</v>
+        <v>109</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E62" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="K62" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>44</v>
+        <v>313</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>303</v>
+        <v>52</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E63" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="K63" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="D64" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E64" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>319</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>320</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>206</v>
+        <v>243</v>
       </c>
       <c r="K64" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
@@ -4585,19 +4678,19 @@
         <v>322</v>
       </c>
       <c r="C65" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E65" s="3">
+        <v>4</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E65" s="3">
-        <v>3</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>304</v>
-      </c>
       <c r="G65" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>31</v>
@@ -4606,33 +4699,33 @@
         <v>324</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="K65" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="C66" s="3" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E66" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>31</v>
@@ -4641,115 +4734,568 @@
         <v>326</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="K66" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>328</v>
-      </c>
       <c r="C67" s="3" t="s">
-        <v>329</v>
+        <v>58</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E67" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>319</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>55</v>
+        <v>243</v>
       </c>
       <c r="K67" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>331</v>
+        <v>44</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>199</v>
+        <v>317</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>204</v>
+        <v>318</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E68" s="3">
-        <v>0</v>
-      </c>
-      <c r="F68" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>319</v>
+      </c>
       <c r="G68" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="K68" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" s="3">
+        <v>3</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I69" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="J69" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="K69" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="B70" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="C70" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="3">
+        <v>3</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K70" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" s="3">
+        <v>3</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="K71" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="K72" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" s="3">
+        <v>3</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="K73" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E74" s="3">
+        <v>3</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="K74" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E75" s="3">
+        <v>3</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="K75" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K76" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E77" s="3">
+        <v>3</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K77" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E78" s="3">
+        <v>3</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K78" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E79" s="3">
+        <v>3</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K79" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E69" s="3">
+      <c r="E80" s="3">
         <v>0</v>
       </c>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H69" s="3" t="s">
+      <c r="F80" s="3"/>
+      <c r="G80" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K80" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H81" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I69" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="K69" s="3">
-        <v>1</v>
+      <c r="I81" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E82" s="3">
+        <v>0</v>
+      </c>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="K82" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K69"/>
+  <autoFilter ref="A1:K82"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4819,6 +5365,19 @@
     <hyperlink ref="I67" r:id="rId66"/>
     <hyperlink ref="I68" r:id="rId67"/>
     <hyperlink ref="I69" r:id="rId68"/>
+    <hyperlink ref="I70" r:id="rId69"/>
+    <hyperlink ref="I71" r:id="rId70"/>
+    <hyperlink ref="I72" r:id="rId71"/>
+    <hyperlink ref="I73" r:id="rId72"/>
+    <hyperlink ref="I74" r:id="rId73"/>
+    <hyperlink ref="I75" r:id="rId74"/>
+    <hyperlink ref="I76" r:id="rId75"/>
+    <hyperlink ref="I77" r:id="rId76"/>
+    <hyperlink ref="I78" r:id="rId77"/>
+    <hyperlink ref="I79" r:id="rId78"/>
+    <hyperlink ref="I80" r:id="rId79"/>
+    <hyperlink ref="I81" r:id="rId80"/>
+    <hyperlink ref="I82" r:id="rId81"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4827,8 +5386,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4849,10 +5408,10 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>43</v>
@@ -4860,79 +5419,79 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>114</v>
+        <v>180</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>116</v>
+        <v>182</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>117</v>
+        <v>183</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>140</v>
+        <v>202</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>141</v>
+        <v>203</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>142</v>
+        <v>205</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>143</v>
+        <v>206</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>240</v>
+        <v>109</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
@@ -4941,63 +5500,107 @@
         <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>321</v>
+        <v>139</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>322</v>
+        <v>248</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>304</v>
+        <v>250</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>324</v>
+        <v>251</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>325</v>
+        <v>259</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>114</v>
+        <v>260</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>304</v>
+        <v>250</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>326</v>
+        <v>261</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>107</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3">
+        <v>6</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G9"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5005,6 +5608,8 @@
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
     <hyperlink ref="F7" r:id="rId6"/>
+    <hyperlink ref="F8" r:id="rId7"/>
+    <hyperlink ref="F9" r:id="rId8"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5019,178 +5624,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>337</v>
+        <v>369</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>338</v>
+        <v>370</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>339</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="B2" s="3">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>340</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>312</v>
+        <v>373</v>
       </c>
       <c r="B3" s="3">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>341</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>342</v>
+        <v>375</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>343</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>319</v>
+        <v>377</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>344</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="B6" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>347</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>349</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>351</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>308</v>
+        <v>383</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>352</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>353</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>354</v>
+        <v>332</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>355</v>
+        <v>386</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>356</v>
+        <v>387</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>357</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>358</v>
+        <v>389</v>
       </c>
       <c r="B14" s="3">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>359</v>
+        <v>390</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>360</v>
+        <v>391</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>361</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>362</v>
+        <v>393</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>363</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -5210,10 +5815,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>364</v>
+        <v>395</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>365</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2">
@@ -5221,10 +5826,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
     </row>
     <row r="3">
@@ -5232,10 +5837,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>367</v>
+        <v>398</v>
       </c>
     </row>
     <row r="4">
@@ -5243,10 +5848,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>368</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5">
@@ -5257,7 +5862,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>369</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6">
@@ -5268,7 +5873,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>370</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -5289,13 +5894,13 @@
         <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>372</v>
+        <v>403</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>373</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2">
@@ -5303,10 +5908,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>374</v>
+        <v>405</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5315,10 +5920,10 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>374</v>
+        <v>405</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -5330,7 +5935,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>374</v>
+        <v>405</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W25.xlsx
+++ b/reports/devops-juniors-israel-2026-W25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="390">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-17T11:15:19</t>
+    <t xml:space="preserve">2026-06-18T10:45:34</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -184,996 +184,948 @@
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
+    <t xml:space="preserve">SW DevOps and Test Infrastructure Student, Nitro SW Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Terraform/IaC, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sw-devops-and-test-infrastructure-student-nitro-sw-team-at-amazon-web-services-aws-4425403074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (36613)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-36613-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428823042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - JB-651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux Software Embedded Engineer (Junior position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDA Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-software-embedded-engineer-junior-position-at-mda-space-4422723139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (24892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4427356844</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plarium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-administrator-at-plarium-4402847792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-extreme-4426743545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist - JB-594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-jb-594-at-pwc-israel-4429922813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassesUSA.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4400413150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accel Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-accel-solutions-4427341027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpotNet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spotnet-4426875292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4425818718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elspec Engineering ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INNERGY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toronto, Toronto, Ontario, Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-technical-support-specialist-innergy-1133586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk - 239819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excis Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4429959640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demo Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/demo-support-engineer-at-walkme-4429569657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4423670353</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-12</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-ai-4427315937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bria AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (36613)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-36613-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428823042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-administrator-at-check-point-software-4427626178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMAREL LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux Software Embedded Engineer (Junior position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDA Space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-software-embedded-engineer-junior-position-at-mda-space-4422723139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategy Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-systems-engineer-at-ben-gurion-university-of-the-negev-4428645689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plarium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-administrator-at-plarium-4402847792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intezer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4425470752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician (34817)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-34817-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428805862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Support &amp; Systems Operations Specialist- position no. 1601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-support-systems-operations-specialist-position-no-1601-at-ibi-investment-house-4423609880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Become a Student Life Coach Flexible Role UK Â£20 Â£40 hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-become-a-student-life-coach-flexible-role-uk-20-40-hr-findtutors-1133462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-sela-4426498040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GlassesUSA.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4400413150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpotNet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spotnet-4426875292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accel Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-accel-solutions-4427341027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4425818718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk - 239819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragontail Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4422278367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Representative (Full-Time, On-Site | Be’er Sheva – Gav Yam Park)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SITE123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-representative-full-time-on-site-be%E2%80%99er-sheva-%E2%80%93-gav-yam-park-at-site123-4419228442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innocom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-innocom-4427324663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4423614421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4419979615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician (34817)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-34817-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428805862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4425470752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Support &amp; Systems Operations Specialist- position no. 1601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBI Investment House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-support-systems-operations-specialist-position-no-1601-at-ibi-investment-house-4423609880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-south-apac-sea-anz-ind-subcont-4390170199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unframe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-unframe-4425465742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-4417759260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Become a Student Life Coach Flexible Role UK Â£20 Â£40 hr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-become-a-student-life-coach-flexible-role-uk-20-40-hr-findtutors-1133462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Advisor Evenings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walden University</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columbia, Columbia, Maryland, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-advisor-evenings-walden-university-1133418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
@@ -1183,16 +1135,16 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
-  </si>
-  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">Docker</t>
@@ -1356,7 +1308,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -1364,7 +1316,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1372,7 +1324,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -1380,7 +1332,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>276</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -1462,7 +1414,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
@@ -1470,7 +1422,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -1478,7 +1430,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1512,7 +1464,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29">
@@ -1660,10 +1612,10 @@
         <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>59</v>
@@ -1689,25 +1641,25 @@
         <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F5" s="3">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -1715,31 +1667,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="3">
         <v>68</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="3">
-        <v>57</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
@@ -1747,31 +1699,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -1779,13 +1731,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>26</v>
@@ -1811,7 +1763,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>82</v>
@@ -1849,25 +1801,25 @@
         <v>87</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="3">
+        <v>44</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="3">
-        <v>47</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
@@ -1875,13 +1827,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>25</v>
@@ -1890,16 +1842,16 @@
         <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -1907,31 +1859,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -1939,31 +1891,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="3">
+        <v>30</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="3">
-        <v>44</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>102</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -1971,31 +1923,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="3">
+        <v>30</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="3">
-        <v>40</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="15">
@@ -2009,25 +1961,25 @@
         <v>110</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -2035,19 +1987,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>117</v>
@@ -2073,25 +2025,25 @@
         <v>121</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="3">
+        <v>27</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="3">
-        <v>32</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
@@ -2099,31 +2051,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="E18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="3">
+        <v>27</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="3">
-        <v>32</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19">
@@ -2131,31 +2083,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>131</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>132</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20">
@@ -2163,31 +2115,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3">
+        <v>26</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="3">
-        <v>30</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -2195,31 +2147,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="3">
+        <v>24</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="3">
-        <v>30</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>144</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22">
@@ -2227,31 +2179,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
@@ -2259,31 +2211,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>144</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
@@ -2291,31 +2243,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="3">
+        <v>18</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="3">
-        <v>27</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="25">
@@ -2323,31 +2275,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F25" s="3">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="26">
@@ -2355,31 +2307,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="D26" s="3" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2418,8 +2370,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2432,7 +2384,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -2447,22 +2399,22 @@
         <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2">
@@ -2485,7 +2437,7 @@
         <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2497,7 +2449,7 @@
         <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -2520,7 +2472,7 @@
         <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2532,7 +2484,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -2546,16 +2498,16 @@
         <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2567,7 +2519,7 @@
         <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2578,112 +2530,112 @@
         <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E5" s="3">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K5" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3">
         <v>68</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="3">
-        <v>57</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="K6" s="3">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="K7" s="3">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>26</v>
@@ -2695,7 +2647,7 @@
         <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
@@ -2707,12 +2659,12 @@
         <v>81</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>82</v>
@@ -2730,7 +2682,7 @@
         <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2742,7 +2694,7 @@
         <v>49</v>
       </c>
       <c r="K9" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -2753,42 +2705,42 @@
         <v>87</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="3">
+        <v>44</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="3">
-        <v>47</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K10" s="3">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="C11" s="3" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>25</v>
@@ -2797,127 +2749,127 @@
         <v>44</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K11" s="3">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K12" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="3">
+        <v>30</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="3">
-        <v>44</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="G13" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>102</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="K13" s="3">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="3">
+        <v>30</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="3">
-        <v>40</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="K14" s="3">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -2928,54 +2880,54 @@
         <v>110</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K15" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>117</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
@@ -2987,7 +2939,7 @@
         <v>119</v>
       </c>
       <c r="K16" s="3">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
@@ -2998,579 +2950,579 @@
         <v>121</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="3">
+        <v>27</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="3">
-        <v>32</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="K17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="D18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="3">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="3">
-        <v>32</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="K18" s="3">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>131</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>132</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="K19" s="3">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="3">
+        <v>26</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="3">
-        <v>30</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="K20" s="3">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="3">
+        <v>24</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3">
-        <v>30</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>144</v>
+        <v>61</v>
       </c>
       <c r="K21" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="K22" s="3">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>144</v>
+        <v>49</v>
       </c>
       <c r="K23" s="3">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="3">
+        <v>18</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="3">
-        <v>27</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="K24" s="3">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E25" s="3">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F25" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="K25" s="3">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="C26" s="3" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="K26" s="3">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>101</v>
+        <v>174</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>174</v>
+        <v>61</v>
       </c>
       <c r="K27" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>49</v>
       </c>
       <c r="K28" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>126</v>
+        <v>181</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E29" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="K29" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>62</v>
+        <v>187</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="3">
+        <v>13</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30" s="3">
-        <v>20</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="G30" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>49</v>
+        <v>190</v>
       </c>
       <c r="K30" s="3">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E31" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K31" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>195</v>
+        <v>52</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>197</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="K32" s="3">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>56</v>
+        <v>198</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>199</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>189</v>
+        <v>52</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>200</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
@@ -3582,39 +3534,39 @@
         <v>49</v>
       </c>
       <c r="K33" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="3">
+        <v>13</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="G34" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" s="3">
-        <v>16</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="K34" s="3">
         <v>0</v>
@@ -3622,42 +3574,42 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>209</v>
+        <v>64</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3">
         <v>13</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="K35" s="3">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>213</v>
+        <v>177</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>208</v>
@@ -3666,144 +3618,144 @@
         <v>209</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F36" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>214</v>
-      </c>
       <c r="J36" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="K36" s="3">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="3">
+        <v>10</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" s="3">
-        <v>13</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="J37" s="3" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="K37" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>220</v>
+        <v>62</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>52</v>
+        <v>217</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>49</v>
+        <v>186</v>
       </c>
       <c r="K38" s="3">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>225</v>
+        <v>138</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="K39" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3812,33 +3764,33 @@
         <v>10</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="K40" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>109</v>
+        <v>228</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>233</v>
+        <v>70</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
@@ -3850,16 +3802,16 @@
         <v>230</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="K41" s="3">
         <v>24</v>
@@ -3867,13 +3819,13 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>109</v>
+        <v>232</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>122</v>
+        <v>234</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
@@ -3882,22 +3834,22 @@
         <v>10</v>
       </c>
       <c r="F42" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I42" s="3" t="s">
+      <c r="J42" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="K42" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -3908,7 +3860,7 @@
         <v>239</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>240</v>
+        <v>92</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
@@ -3917,33 +3869,33 @@
         <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="J43" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="K43" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>244</v>
+        <v>109</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>58</v>
+        <v>243</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3952,33 +3904,33 @@
         <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="K44" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>249</v>
+        <v>70</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3987,33 +3939,33 @@
         <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="K45" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>62</v>
+        <v>247</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>58</v>
+        <v>249</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
@@ -4022,33 +3974,33 @@
         <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="K46" s="3">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
@@ -4057,33 +4009,33 @@
         <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>258</v>
+        <v>190</v>
       </c>
       <c r="K47" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>101</v>
+        <v>258</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
@@ -4092,19 +4044,19 @@
         <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -4112,34 +4064,34 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="C49" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" s="3">
+        <v>8</v>
+      </c>
+      <c r="F49" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="G49" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49" s="3">
-        <v>10</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>265</v>
-      </c>
       <c r="J49" s="3" t="s">
-        <v>98</v>
+        <v>237</v>
       </c>
       <c r="K49" s="3">
         <v>3</v>
@@ -4147,13 +4099,13 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>126</v>
+        <v>265</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>266</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>101</v>
+        <v>267</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>26</v>
@@ -4162,68 +4114,68 @@
         <v>8</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>258</v>
+        <v>186</v>
       </c>
       <c r="K50" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>269</v>
+        <v>172</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" s="3">
+        <v>6</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="G51" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E51" s="3">
-        <v>8</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>273</v>
-      </c>
       <c r="J51" s="3" t="s">
-        <v>232</v>
+        <v>193</v>
       </c>
       <c r="K51" s="3">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>159</v>
+        <v>273</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4232,33 +4184,33 @@
         <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>276</v>
-      </c>
       <c r="J52" s="3" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="K52" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>278</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4267,22 +4219,22 @@
         <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I53" s="3" t="s">
+      <c r="J53" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="J53" s="3" t="s">
-        <v>258</v>
-      </c>
       <c r="K53" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54">
@@ -4302,19 +4254,19 @@
         <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>174</v>
+        <v>286</v>
       </c>
       <c r="K54" s="3">
         <v>22</v>
@@ -4322,13 +4274,13 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4337,33 +4289,33 @@
         <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>290</v>
+        <v>114</v>
       </c>
       <c r="K55" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4372,10 +4324,10 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
@@ -4384,10 +4336,10 @@
         <v>294</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>144</v>
+        <v>190</v>
       </c>
       <c r="K56" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57">
@@ -4398,7 +4350,7 @@
         <v>296</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>58</v>
+        <v>243</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
@@ -4407,10 +4359,10 @@
         <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>31</v>
@@ -4419,21 +4371,21 @@
         <v>297</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>212</v>
+        <v>61</v>
       </c>
       <c r="K57" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>109</v>
+        <v>256</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>298</v>
+        <v>134</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
@@ -4442,33 +4394,33 @@
         <v>6</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="K58" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
@@ -4477,33 +4429,33 @@
         <v>6</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="K59" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>304</v>
+        <v>62</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
@@ -4512,33 +4464,33 @@
         <v>6</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>192</v>
+        <v>251</v>
       </c>
       <c r="K60" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>204</v>
+        <v>70</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>25</v>
@@ -4547,103 +4499,103 @@
         <v>6</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K61" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>109</v>
+        <v>309</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="D62" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E62" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="K62" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>52</v>
+        <v>126</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E63" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>272</v>
+        <v>316</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>174</v>
+        <v>103</v>
       </c>
       <c r="K63" s="3">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>318</v>
+        <v>92</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>26</v>
@@ -4652,115 +4604,115 @@
         <v>4</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>243</v>
+        <v>322</v>
       </c>
       <c r="K64" s="3">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>321</v>
+        <v>44</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>151</v>
+        <v>311</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E65" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F65" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I65" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G65" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>324</v>
-      </c>
       <c r="J65" s="3" t="s">
-        <v>133</v>
+        <v>186</v>
       </c>
       <c r="K65" s="3">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E66" s="3">
-        <v>4</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>319</v>
-      </c>
       <c r="G66" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>119</v>
+        <v>186</v>
       </c>
       <c r="K66" s="3">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="3">
+        <v>3</v>
+      </c>
+      <c r="F67" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E67" s="3">
-        <v>4</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>319</v>
-      </c>
       <c r="G67" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>31</v>
@@ -4769,21 +4721,21 @@
         <v>328</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>243</v>
+        <v>280</v>
       </c>
       <c r="K67" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>44</v>
+        <v>329</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>25</v>
@@ -4792,33 +4744,33 @@
         <v>3</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>232</v>
+        <v>100</v>
       </c>
       <c r="K68" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
@@ -4827,33 +4779,33 @@
         <v>3</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="K69" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>334</v>
+        <v>109</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>101</v>
+        <v>289</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>25</v>
@@ -4862,33 +4814,33 @@
         <v>3</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>212</v>
+        <v>103</v>
       </c>
       <c r="K70" s="3">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>339</v>
+        <v>96</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>340</v>
+        <v>97</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>25</v>
@@ -4897,33 +4849,33 @@
         <v>3</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K71" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>342</v>
+        <v>256</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>121</v>
+        <v>341</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>25</v>
@@ -4932,33 +4884,33 @@
         <v>3</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="K72" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>224</v>
+        <v>343</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>344</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>345</v>
+        <v>92</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>25</v>
@@ -4967,10 +4919,10 @@
         <v>3</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>31</v>
@@ -4979,33 +4931,31 @@
         <v>346</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>198</v>
+        <v>322</v>
       </c>
       <c r="K73" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>139</v>
+        <v>347</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>347</v>
+        <v>182</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>116</v>
+        <v>188</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E74" s="3">
-        <v>3</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>319</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>31</v>
@@ -5014,288 +4964,47 @@
         <v>348</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>133</v>
+        <v>190</v>
       </c>
       <c r="K74" s="3">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>109</v>
+        <v>349</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>58</v>
+        <v>351</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E75" s="3">
-        <v>3</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>323</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="K75" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E76" s="3">
-        <v>3</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="K76" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E77" s="3">
-        <v>3</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="K77" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E78" s="3">
-        <v>3</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K78" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E79" s="3">
-        <v>3</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="K79" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E80" s="3">
-        <v>0</v>
-      </c>
-      <c r="F80" s="3"/>
-      <c r="G80" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="J80" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="K80" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
-      <c r="F81" s="3"/>
-      <c r="G81" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E82" s="3">
-        <v>0</v>
-      </c>
-      <c r="F82" s="3"/>
-      <c r="G82" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="K82" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K82"/>
+  <autoFilter ref="A1:K75"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5371,13 +5080,6 @@
     <hyperlink ref="I73" r:id="rId72"/>
     <hyperlink ref="I74" r:id="rId73"/>
     <hyperlink ref="I75" r:id="rId74"/>
-    <hyperlink ref="I76" r:id="rId75"/>
-    <hyperlink ref="I77" r:id="rId76"/>
-    <hyperlink ref="I78" r:id="rId77"/>
-    <hyperlink ref="I79" r:id="rId78"/>
-    <hyperlink ref="I80" r:id="rId79"/>
-    <hyperlink ref="I81" r:id="rId80"/>
-    <hyperlink ref="I82" r:id="rId81"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5385,8 +5087,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="1" max="1" width="58" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -5408,10 +5110,10 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>43</v>
@@ -5419,188 +5121,259 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>126</v>
+        <v>68</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>180</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>182</v>
+        <v>71</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>183</v>
+        <v>72</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>202</v>
+        <v>120</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>203</v>
+        <v>121</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>205</v>
+        <v>122</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>206</v>
+        <v>123</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>235</v>
+        <v>138</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>236</v>
+        <v>139</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>237</v>
+        <v>140</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>248</v>
+        <v>162</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>250</v>
+        <v>164</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>251</v>
+        <v>165</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>259</v>
+        <v>172</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>260</v>
+        <v>173</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>261</v>
+        <v>176</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>311</v>
+        <v>202</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>293</v>
+        <v>203</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>312</v>
+        <v>204</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>361</v>
+        <v>219</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>362</v>
+        <v>138</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>220</v>
+      </c>
       <c r="F9" s="3" t="s">
-        <v>364</v>
+        <v>221</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>81</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="3">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
+        <v>6</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="3">
+        <v>6</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G12"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5610,6 +5383,9 @@
     <hyperlink ref="F7" r:id="rId6"/>
     <hyperlink ref="F8" r:id="rId7"/>
     <hyperlink ref="F9" r:id="rId8"/>
+    <hyperlink ref="F10" r:id="rId9"/>
+    <hyperlink ref="F11" r:id="rId10"/>
+    <hyperlink ref="F12" r:id="rId11"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5624,178 +5400,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B2" s="3">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="B3" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>377</v>
+        <v>335</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="B10" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>236</v>
+        <v>345</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -5815,10 +5591,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2">
@@ -5826,10 +5602,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3">
@@ -5837,10 +5613,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4">
@@ -5848,10 +5624,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5">
@@ -5862,7 +5638,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>400</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6">
@@ -5873,7 +5649,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>401</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -5894,13 +5670,13 @@
         <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
@@ -5911,7 +5687,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5920,10 +5696,10 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -5935,7 +5711,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W25.xlsx
+++ b/reports/devops-juniors-israel-2026-W25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="402">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-18T10:45:34</t>
+    <t xml:space="preserve">2026-06-19T10:55:54</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -106,6 +106,9 @@
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -166,6 +169,24 @@
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior AI SRE Developer</t>
   </si>
   <si>
@@ -184,961 +205,982 @@
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
-    <t xml:space="preserve">SW DevOps and Test Infrastructure Student, Nitro SW Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Terraform/IaC, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sw-devops-and-test-infrastructure-student-nitro-sw-team-at-amazon-web-services-aws-4425403074</t>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-18</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer – Microsoft Infrastructure &amp; Cloud (Help Desk + 3rd Tier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G-MEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-%E2%80%93-microsoft-infrastructure-cloud-help-desk-%2B-3rd-tier-at-g-mel-4429114041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact Networks Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eilat, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-impact-networks-group-4429545054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker, Kubernetes, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-dream-4427425550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - JB-651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
     <t xml:space="preserve">Technical Support Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux Software Embedded Engineer (Junior position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDA Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-software-embedded-engineer-junior-position-at-mda-space-4422723139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (24892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4427356844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Eng.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultra Information Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-eng-at-ultra-information-solutions-4412395476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-monday-com-4430722480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plarium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-administrator-at-plarium-4402847792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cross-river-4408813327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist - JB-594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-jb-594-at-pwc-israel-4429922813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpotNet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spotnet-4426875292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4425818718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Representative - CCTV &amp; Smart Home Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RISCO Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-representative-cctv-smart-home-systems-at-risco-group-4429281171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipalti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databases, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-tipalti-4417387930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INNERGY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toronto, Toronto, Ontario, Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-technical-support-specialist-innergy-1133586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excis Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4429959640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk - 239819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-29</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (36613)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-36613-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428823042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - JB-651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux Software Embedded Engineer (Junior position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDA Space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-software-embedded-engineer-junior-position-at-mda-space-4422723139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategy Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (24892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4427356844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
+    <t xml:space="preserve">Zoho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Representative (Full-Time, On-Site | Be’er Sheva – Gav Yam Park)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SITE123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-representative-full-time-on-site-be%E2%80%99er-sheva-%E2%80%93-gav-yam-park-at-site123-4419228442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenius Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colorado,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-help-desk-zenius-corporation-1133680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4423670353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4427828397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4425470752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unframe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-unframe-4425465742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-4417759260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סטודנט/ית למחלקת התכנון</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safed, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%A1%D7%98%D7%95%D7%93%D7%A0%D7%98-%D7%99%D7%AA-%D7%9C%D7%9E%D7%97%D7%9C%D7%A7%D7%AA-%D7%94%D7%AA%D7%9B%D7%A0%D7%95%D7%9F-at-unilever-4426489234</t>
   </si>
   <si>
     <t xml:space="preserve">Nova Ltd.</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
+    <t xml:space="preserve">yes</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
   </si>
   <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plarium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-administrator-at-plarium-4402847792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-extreme-4426743545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist - JB-594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-jb-594-at-pwc-israel-4429922813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GlassesUSA.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4400413150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accel Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-accel-solutions-4427341027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpotNet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spotnet-4426875292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4425818718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elspec Engineering ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INNERGY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toronto, Toronto, Ontario, Canada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-technical-support-specialist-innergy-1133586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk - 239819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excis Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4429959640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demo Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/demo-support-engineer-at-walkme-4429569657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4423670353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4425470752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician (34817)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-34817-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428805862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Support &amp; Systems Operations Specialist- position no. 1601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBI Investment House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-support-systems-operations-specialist-position-no-1601-at-ibi-investment-house-4423609880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Become a Student Life Coach Flexible Role UK Â£20 Â£40 hr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-become-a-student-life-coach-flexible-role-uk-20-40-hr-findtutors-1133462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
     <t xml:space="preserve">Kubernetes</t>
@@ -1147,12 +1189,6 @@
     <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
     <t xml:space="preserve">Count</t>
   </si>
   <si>
@@ -1174,6 +1210,9 @@
     <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
   </si>
   <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jobs</t>
   </si>
   <si>
@@ -1181,9 +1220,6 @@
   </si>
   <si>
     <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
   </si>
 </sst>
 </file>
@@ -1308,7 +1344,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -1316,7 +1352,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1324,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -1332,7 +1368,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>287</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -1414,7 +1450,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
@@ -1422,7 +1458,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -1430,7 +1466,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1446,33 +1482,33 @@
         <v>29</v>
       </c>
       <c r="B25" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-    </row>
     <row r="27">
-      <c r="A27" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="A27" s="3"/>
       <c r="B27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="3">
-        <v>62</v>
-      </c>
+      <c r="B28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>10</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30">
@@ -1480,6 +1516,14 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="3">
         <v>2</v>
       </c>
     </row>
@@ -1492,7 +1536,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1504,34 +1548,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
@@ -1539,13 +1583,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>25</v>
@@ -1554,16 +1598,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -1571,31 +1615,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
@@ -1603,31 +1647,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -1635,31 +1679,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F5" s="3">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -1667,31 +1711,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>71</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -1705,25 +1749,25 @@
         <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1731,31 +1775,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1763,13 +1807,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>25</v>
@@ -1778,16 +1822,16 @@
         <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -1795,31 +1839,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -1827,31 +1871,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -1859,31 +1903,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F12" s="3">
         <v>32</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -1891,13 +1935,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>25</v>
@@ -1906,16 +1950,16 @@
         <v>30</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14">
@@ -1923,13 +1967,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
@@ -1938,16 +1982,16 @@
         <v>30</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1955,13 +1999,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
@@ -1970,16 +2014,16 @@
         <v>30</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16">
@@ -1987,31 +2031,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17">
@@ -2019,31 +2063,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18">
@@ -2051,31 +2095,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19">
@@ -2083,13 +2127,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
@@ -2098,16 +2142,16 @@
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -2115,31 +2159,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="3">
         <v>27</v>
       </c>
-      <c r="F20" s="3">
-        <v>26</v>
-      </c>
       <c r="G20" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21">
@@ -2147,31 +2191,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="E21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="3">
         <v>26</v>
       </c>
-      <c r="F21" s="3">
-        <v>24</v>
-      </c>
       <c r="G21" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
@@ -2179,13 +2223,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>26</v>
@@ -2194,16 +2238,16 @@
         <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23">
@@ -2211,31 +2255,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
@@ -2243,31 +2287,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25">
@@ -2275,31 +2319,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>160</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
@@ -2307,31 +2351,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F26" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>61</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -2370,7 +2414,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2384,48 +2428,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>25</v>
@@ -2434,162 +2478,162 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E5" s="3">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K5" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -2600,77 +2644,77 @@
         <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E7" s="3">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="K8" s="3">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>25</v>
@@ -2679,138 +2723,138 @@
         <v>47</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E10" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E12" s="3">
         <v>32</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>25</v>
@@ -2819,33 +2863,33 @@
         <v>30</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K13" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
@@ -2854,33 +2898,33 @@
         <v>30</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="K14" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>25</v>
@@ -2889,138 +2933,138 @@
         <v>30</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="K15" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="K16" s="3">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="K17" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="K18" s="3">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
@@ -3029,103 +3073,103 @@
         <v>27</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="K19" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="3">
         <v>27</v>
       </c>
-      <c r="E20" s="3">
-        <v>26</v>
-      </c>
       <c r="F20" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="K20" s="3">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="3">
         <v>26</v>
       </c>
-      <c r="E21" s="3">
-        <v>24</v>
-      </c>
       <c r="F21" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="K21" s="3">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>26</v>
@@ -3134,313 +3178,313 @@
         <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="K22" s="3">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K23" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="K24" s="3">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="K25" s="3">
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E26" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>61</v>
+        <v>167</v>
       </c>
       <c r="K26" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E27" s="3">
         <v>17</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>61</v>
+        <v>179</v>
       </c>
       <c r="K27" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="K28" s="3">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>186</v>
+        <v>68</v>
       </c>
       <c r="K29" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>188</v>
+        <v>90</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="K30" s="3">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>27</v>
@@ -3449,103 +3493,103 @@
         <v>13</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="K31" s="3">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>195</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E32" s="3">
         <v>13</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="K32" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E33" s="3">
         <v>13</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>49</v>
+        <v>205</v>
       </c>
       <c r="K33" s="3">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>62</v>
+        <v>206</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>163</v>
+        <v>208</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3554,33 +3598,33 @@
         <v>13</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="K34" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>116</v>
+        <v>212</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
@@ -3589,173 +3633,173 @@
         <v>13</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>207</v>
+        <v>56</v>
       </c>
       <c r="K35" s="3">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>209</v>
+        <v>65</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>184</v>
+        <v>217</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>211</v>
+        <v>104</v>
       </c>
       <c r="K36" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>214</v>
+        <v>59</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>186</v>
+        <v>50</v>
       </c>
       <c r="K37" s="3">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>186</v>
+        <v>104</v>
       </c>
       <c r="K38" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>138</v>
+        <v>228</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>70</v>
+        <v>208</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E39" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>61</v>
+        <v>230</v>
       </c>
       <c r="K39" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3764,33 +3808,33 @@
         <v>10</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>227</v>
+        <v>199</v>
       </c>
       <c r="K40" s="3">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>228</v>
+        <v>153</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>70</v>
+        <v>236</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
@@ -3799,33 +3843,33 @@
         <v>10</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="K41" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
@@ -3834,33 +3878,33 @@
         <v>10</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="K42" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>239</v>
+        <v>146</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
@@ -3869,19 +3913,19 @@
         <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>241</v>
+        <v>68</v>
       </c>
       <c r="K43" s="3">
         <v>1</v>
@@ -3889,13 +3933,13 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3904,33 +3948,33 @@
         <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="K44" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>68</v>
+        <v>251</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>70</v>
+        <v>253</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3939,33 +3983,33 @@
         <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>186</v>
+        <v>255</v>
       </c>
       <c r="K45" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
@@ -3974,33 +4018,33 @@
         <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>251</v>
+        <v>104</v>
       </c>
       <c r="K46" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>252</v>
+        <v>153</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>254</v>
+        <v>147</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
@@ -4009,33 +4053,33 @@
         <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>225</v>
+        <v>260</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>190</v>
+        <v>104</v>
       </c>
       <c r="K47" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>256</v>
+        <v>82</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
@@ -4044,33 +4088,33 @@
         <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="K48" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>26</v>
@@ -4079,33 +4123,33 @@
         <v>8</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="K49" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>26</v>
@@ -4114,33 +4158,33 @@
         <v>8</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="K50" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>134</v>
+        <v>275</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>97</v>
+        <v>276</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
@@ -4149,33 +4193,33 @@
         <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="K51" s="3">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>97</v>
+        <v>281</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4184,33 +4228,33 @@
         <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>237</v>
+        <v>284</v>
       </c>
       <c r="K52" s="3">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>277</v>
+        <v>142</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>278</v>
+        <v>129</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4219,33 +4263,33 @@
         <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>280</v>
+        <v>77</v>
       </c>
       <c r="K53" s="3">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4254,33 +4298,33 @@
         <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>286</v>
+        <v>87</v>
       </c>
       <c r="K54" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>289</v>
+        <v>65</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4289,33 +4333,33 @@
         <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="K55" s="3">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>292</v>
+        <v>185</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>293</v>
+        <v>142</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4324,33 +4368,33 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="K56" s="3">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>296</v>
-      </c>
       <c r="C57" s="3" t="s">
-        <v>243</v>
+        <v>129</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
@@ -4359,33 +4403,33 @@
         <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>270</v>
+        <v>296</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>297</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>61</v>
+        <v>243</v>
       </c>
       <c r="K57" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>256</v>
+        <v>298</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>134</v>
+        <v>299</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>97</v>
+        <v>248</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
@@ -4394,33 +4438,33 @@
         <v>6</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="K58" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>70</v>
+        <v>303</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
@@ -4429,33 +4473,33 @@
         <v>6</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>67</v>
+        <v>305</v>
       </c>
       <c r="K59" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>62</v>
+        <v>306</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
@@ -4464,33 +4508,33 @@
         <v>6</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>251</v>
+        <v>309</v>
       </c>
       <c r="K60" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>305</v>
+        <v>153</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>25</v>
@@ -4499,103 +4543,103 @@
         <v>6</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>61</v>
+        <v>255</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E62" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>312</v>
+        <v>273</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>227</v>
+        <v>62</v>
       </c>
       <c r="K62" s="3">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>314</v>
+        <v>185</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>126</v>
+        <v>318</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E63" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K63" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>92</v>
+        <v>323</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>26</v>
@@ -4604,138 +4648,138 @@
         <v>4</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="K64" s="3">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>44</v>
+        <v>327</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>311</v>
+        <v>90</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E65" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>186</v>
+        <v>107</v>
       </c>
       <c r="K65" s="3">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>62</v>
+        <v>331</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E66" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>186</v>
+        <v>335</v>
       </c>
       <c r="K66" s="3">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E67" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>280</v>
+        <v>104</v>
       </c>
       <c r="K67" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>329</v>
+        <v>45</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>25</v>
@@ -4744,33 +4788,33 @@
         <v>3</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>100</v>
+        <v>199</v>
       </c>
       <c r="K68" s="3">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
@@ -4779,33 +4823,33 @@
         <v>3</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="K69" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>109</v>
+        <v>343</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>289</v>
+        <v>224</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>25</v>
@@ -4814,33 +4858,33 @@
         <v>3</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="K70" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>339</v>
+        <v>113</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>96</v>
+        <v>346</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>25</v>
@@ -4849,33 +4893,33 @@
         <v>3</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="K71" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>256</v>
+        <v>153</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>25</v>
@@ -4884,33 +4928,33 @@
         <v>3</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="K72" s="3">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>343</v>
+        <v>118</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>25</v>
@@ -4919,66 +4963,68 @@
         <v>3</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>322</v>
+        <v>167</v>
       </c>
       <c r="K73" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>347</v>
+        <v>45</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>182</v>
+        <v>352</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>188</v>
+        <v>65</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E74" s="3">
-        <v>0</v>
-      </c>
-      <c r="F74" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>324</v>
+      </c>
       <c r="G74" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="K74" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>27</v>
@@ -4988,23 +5034,89 @@
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>241</v>
+        <v>104</v>
       </c>
       <c r="K75" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E76" s="3">
+        <v>0</v>
+      </c>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K76" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E77" s="3">
+        <v>0</v>
+      </c>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="K77" s="3">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K75"/>
+  <autoFilter ref="A1:K77"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5080,6 +5192,8 @@
     <hyperlink ref="I73" r:id="rId72"/>
     <hyperlink ref="I74" r:id="rId73"/>
     <hyperlink ref="I75" r:id="rId74"/>
+    <hyperlink ref="I76" r:id="rId75"/>
+    <hyperlink ref="I77" r:id="rId76"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5087,8 +5201,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="58" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -5098,282 +5212,234 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D2" s="3">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>68</v>
+        <v>118</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>120</v>
+        <v>215</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>121</v>
+        <v>216</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>122</v>
+        <v>217</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>123</v>
+        <v>218</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>138</v>
+        <v>223</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>139</v>
+        <v>225</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>140</v>
+        <v>226</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>161</v>
+        <v>256</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>162</v>
+        <v>257</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>164</v>
+        <v>241</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>165</v>
+        <v>258</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>173</v>
+        <v>259</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>175</v>
+        <v>260</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>176</v>
+        <v>261</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>62</v>
+        <v>185</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>202</v>
+        <v>317</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>203</v>
+        <v>319</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>204</v>
+        <v>320</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>219</v>
+        <v>321</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>138</v>
+        <v>336</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>220</v>
+        <v>324</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>221</v>
+        <v>337</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>256</v>
+        <v>354</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>257</v>
+        <v>355</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10" s="3">
-        <v>10</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>259</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="3">
-        <v>6</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="3">
-        <v>6</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5384,8 +5450,6 @@
     <hyperlink ref="F8" r:id="rId7"/>
     <hyperlink ref="F9" r:id="rId8"/>
     <hyperlink ref="F10" r:id="rId9"/>
-    <hyperlink ref="F11" r:id="rId10"/>
-    <hyperlink ref="F12" r:id="rId11"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5400,178 +5464,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B2" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="B3" s="3">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B5" s="3">
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>316</v>
+        <v>371</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>184</v>
+        <v>373</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>363</v>
+        <v>197</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>365</v>
+        <v>329</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>327</v>
+        <v>381</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="B16" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -5588,13 +5652,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2">
@@ -5602,10 +5666,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3">
@@ -5613,10 +5677,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4">
@@ -5624,10 +5688,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5">
@@ -5638,7 +5702,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6">
@@ -5646,10 +5710,21 @@
         <v>29</v>
       </c>
       <c r="B6" s="3">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>385</v>
+      <c r="C7" s="3" t="s">
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -5667,51 +5742,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3">
         <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>389</v>
+        <v>359</v>
       </c>
       <c r="D2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>389</v>
+        <v>359</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>389</v>
+        <v>359</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W25.xlsx
+++ b/reports/devops-juniors-israel-2026-W25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="387">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-19T10:55:54</t>
+    <t xml:space="preserve">2026-06-21T10:04:23</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -103,12 +103,12 @@
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -205,768 +205,738 @@
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-18</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - JB-651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux Software Embedded Engineer (Junior position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDA Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-software-embedded-engineer-junior-position-at-mda-space-4422723139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-monday-com-4430722480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plarium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-administrator-at-plarium-4402847792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist - JB-594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-jb-594-at-pwc-israel-4429922813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4425818718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elspec Engineering ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pathway Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toronto, Toronto, Ontario, Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-desktop-support-technician-pathway-communications-1133710</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
   </si>
   <si>
     <t xml:space="preserve">Technical Support Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer – Microsoft Infrastructure &amp; Cloud (Help Desk + 3rd Tier)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-MEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-%E2%80%93-microsoft-infrastructure-cloud-help-desk-%2B-3rd-tier-at-g-mel-4429114041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impact Networks Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eilat, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-impact-networks-group-4429545054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker, Kubernetes, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-dream-4427425550</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - JB-651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux Software Embedded Engineer (Junior position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDA Space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-software-embedded-engineer-junior-position-at-mda-space-4422723139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategy Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (24892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk</t>
   </si>
   <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4427356844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Eng.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultra Information Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-eng-at-ultra-information-solutions-4412395476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-08</t>
   </si>
   <si>
-    <t xml:space="preserve">טכנאי/ת Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-monday-com-4430722480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plarium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-administrator-at-plarium-4402847792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cross-river-4408813327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist - JB-594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-jb-594-at-pwc-israel-4429922813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpotNet</t>
+    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excis Compliance</t>
   </si>
   <si>
     <t xml:space="preserve">Shoham, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spotnet-4426875292</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4429959640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wobi Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-junior-at-wobi-ltd-4419670684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demo Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/demo-support-engineer-at-walkme-4429569657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innocom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-innocom-4427324663</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-17</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4425818718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Representative - CCTV &amp; Smart Home Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RISCO Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-representative-cctv-smart-home-systems-at-risco-group-4429281171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipalti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databases, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-tipalti-4417387930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INNERGY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toronto, Toronto, Ontario, Canada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-technical-support-specialist-innergy-1133586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excis Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4429959640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk - 239819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Representative (Full-Time, On-Site | Be’er Sheva – Gav Yam Park)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SITE123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-representative-full-time-on-site-be%E2%80%99er-sheva-%E2%80%93-gav-yam-park-at-site123-4419228442</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zenius Corporation</t>
   </si>
   <si>
@@ -994,9 +964,6 @@
     <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
     <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
   </si>
   <si>
@@ -1045,37 +1012,34 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
   </si>
   <si>
-    <t xml:space="preserve">Service Desk Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4425470752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unframe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-unframe-4425465742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-4417759260</t>
+    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support &amp; Process Development Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T.E.S GROUP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-process-development-specialist-at-t-e-s-group-4428578923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Support &amp; Systems Operations Specialist- position no. 1601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-support-systems-operations-specialist-position-no-1601-at-ibi-investment-house-4423609880</t>
   </si>
   <si>
     <t xml:space="preserve">סטודנט/ית למחלקת התכנון</t>
@@ -1090,136 +1054,127 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%A1%D7%98%D7%95%D7%93%D7%A0%D7%98-%D7%99%D7%AA-%D7%9C%D7%9E%D7%97%D7%9C%D7%A7%D7%AA-%D7%94%D7%AA%D7%9B%D7%A0%D7%95%D7%9F-at-unilever-4426489234</t>
   </si>
   <si>
-    <t xml:space="preserve">Nova Ltd.</t>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pivot path advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pivot path advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
   </si>
 </sst>
 </file>
@@ -1344,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
@@ -1352,7 +1307,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1360,7 +1315,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -1368,7 +1323,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -1450,7 +1405,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
@@ -1458,7 +1413,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -1466,7 +1421,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1482,7 +1437,7 @@
         <v>29</v>
       </c>
       <c r="B25" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1508,7 +1463,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
@@ -1536,7 +1491,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1624,7 +1579,7 @@
         <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1691,7 +1646,7 @@
         <v>25</v>
       </c>
       <c r="F5" s="3">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>66</v>
@@ -1717,7 +1672,7 @@
         <v>70</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>28</v>
@@ -1726,13 +1681,13 @@
         <v>57</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>50</v>
@@ -1743,10 +1698,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>59</v>
@@ -1758,16 +1713,16 @@
         <v>52</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1775,13 +1730,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
@@ -1790,13 +1745,13 @@
         <v>47</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>50</v>
@@ -1807,31 +1762,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -1839,31 +1794,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -1877,7 +1832,7 @@
         <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>26</v>
@@ -1886,16 +1841,16 @@
         <v>32</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -1903,31 +1858,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="3">
+        <v>30</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="3">
-        <v>32</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -1935,13 +1890,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>25</v>
@@ -1950,16 +1905,16 @@
         <v>30</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -1985,13 +1940,13 @@
         <v>111</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>112</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15">
@@ -1999,19 +1954,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>116</v>
@@ -2023,7 +1978,7 @@
         <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16">
@@ -2031,31 +1986,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17">
@@ -2063,31 +2018,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -2095,31 +2050,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19">
@@ -2127,13 +2082,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
@@ -2142,16 +2097,16 @@
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
@@ -2159,31 +2114,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
@@ -2191,31 +2146,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="3">
+        <v>24</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="3">
-        <v>26</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="22">
@@ -2223,13 +2178,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>26</v>
@@ -2247,7 +2202,7 @@
         <v>149</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
@@ -2258,25 +2213,25 @@
         <v>150</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>50</v>
@@ -2287,31 +2242,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>153</v>
+        <v>79</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>132</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
@@ -2319,31 +2274,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F25" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>50</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26">
@@ -2351,31 +2306,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F26" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -2428,7 +2383,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2443,22 +2398,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2">
@@ -2481,7 +2436,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>33</v>
@@ -2493,7 +2448,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -2507,7 +2462,7 @@
         <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2516,7 +2471,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2528,7 +2483,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -2551,7 +2506,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2563,7 +2518,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -2580,13 +2535,13 @@
         <v>25</v>
       </c>
       <c r="E5" s="3">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2598,7 +2553,7 @@
         <v>68</v>
       </c>
       <c r="K5" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -2609,7 +2564,7 @@
         <v>70</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>28</v>
@@ -2618,30 +2573,30 @@
         <v>57</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K6" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>59</v>
@@ -2653,33 +2608,33 @@
         <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
@@ -2688,92 +2643,92 @@
         <v>47</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K8" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K9" s="3">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E10" s="3">
+        <v>44</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" s="3">
         <v>37</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="K10" s="3">
-        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2784,7 +2739,7 @@
         <v>95</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>26</v>
@@ -2793,68 +2748,68 @@
         <v>32</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K11" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>30</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="3">
-        <v>32</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="K12" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>25</v>
@@ -2863,22 +2818,22 @@
         <v>30</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K13" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -2901,42 +2856,42 @@
         <v>111</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>112</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K14" s="3">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
@@ -2945,77 +2900,77 @@
         <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="K15" s="3">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="K16" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="K17" s="3">
         <v>3</v>
@@ -3023,48 +2978,48 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="K18" s="3">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
@@ -3073,103 +3028,103 @@
         <v>27</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K19" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E20" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="K20" s="3">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="3">
+        <v>24</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="3">
-        <v>26</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="K21" s="3">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>26</v>
@@ -3181,7 +3136,7 @@
         <v>148</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
@@ -3190,10 +3145,10 @@
         <v>149</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="K22" s="3">
-        <v>1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -3201,174 +3156,174 @@
         <v>150</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K23" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>153</v>
+        <v>79</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>132</v>
+        <v>50</v>
       </c>
       <c r="K24" s="3">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E25" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>50</v>
+        <v>163</v>
       </c>
       <c r="K25" s="3">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E26" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K26" s="3">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>179</v>
+        <v>50</v>
       </c>
       <c r="K27" s="3">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28">
@@ -3382,16 +3337,16 @@
         <v>182</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E28" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>183</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
@@ -3400,68 +3355,68 @@
         <v>184</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>68</v>
+        <v>185</v>
       </c>
       <c r="K28" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>187</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E29" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F29" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="J29" s="3" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="K29" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>192</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
@@ -3470,10 +3425,10 @@
         <v>193</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="K30" s="3">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -3484,66 +3439,66 @@
         <v>195</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>196</v>
+        <v>59</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
         <v>13</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="J31" s="3" t="s">
-        <v>199</v>
+        <v>56</v>
       </c>
       <c r="K31" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>201</v>
+        <v>71</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
         <v>13</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="K32" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -3551,39 +3506,39 @@
         <v>203</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>201</v>
+        <v>59</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E33" s="3">
         <v>13</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>205</v>
+        <v>50</v>
       </c>
       <c r="K33" s="3">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>206</v>
+        <v>63</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>207</v>
@@ -3601,7 +3556,7 @@
         <v>209</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>32</v>
@@ -3610,80 +3565,80 @@
         <v>210</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="K34" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" s="3">
+        <v>12</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E35" s="3">
-        <v>13</v>
-      </c>
-      <c r="F35" s="3" t="s">
+      <c r="J35" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="K35" s="3">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>217</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>218</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="K36" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37">
@@ -3694,101 +3649,101 @@
         <v>220</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>59</v>
+        <v>221</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>50</v>
+        <v>224</v>
       </c>
       <c r="K37" s="3">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>118</v>
+        <v>225</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>223</v>
+        <v>144</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>224</v>
+        <v>71</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="K38" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>227</v>
+        <v>79</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>228</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>208</v>
+        <v>71</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
       <c r="K39" s="3">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40">
@@ -3808,33 +3763,33 @@
         <v>10</v>
       </c>
       <c r="F40" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I40" s="3" t="s">
+      <c r="J40" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="K40" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>153</v>
+        <v>236</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
@@ -3843,33 +3798,33 @@
         <v>10</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>199</v>
+        <v>240</v>
       </c>
       <c r="K41" s="3">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
@@ -3878,33 +3833,33 @@
         <v>10</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>243</v>
+        <v>56</v>
       </c>
       <c r="K42" s="3">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>146</v>
+        <v>246</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>65</v>
+        <v>247</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
@@ -3913,278 +3868,278 @@
         <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>68</v>
+        <v>250</v>
       </c>
       <c r="K43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>113</v>
+        <v>251</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>248</v>
+        <v>91</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E44" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="K44" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E45" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>255</v>
+        <v>185</v>
       </c>
       <c r="K45" s="3">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>256</v>
+        <v>194</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="K46" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>153</v>
+        <v>264</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>147</v>
+        <v>266</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>104</v>
+        <v>269</v>
       </c>
       <c r="K47" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>262</v>
+        <v>140</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>263</v>
+        <v>121</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K48" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>243</v>
+        <v>113</v>
       </c>
       <c r="K49" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>272</v>
+        <v>71</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>199</v>
+        <v>56</v>
       </c>
       <c r="K50" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>211</v>
+        <v>279</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>275</v>
+        <v>140</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>276</v>
+        <v>121</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
@@ -4193,33 +4148,33 @@
         <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>199</v>
+        <v>281</v>
       </c>
       <c r="K51" s="3">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4228,33 +4183,33 @@
         <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>284</v>
+        <v>129</v>
       </c>
       <c r="K52" s="3">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>82</v>
+        <v>286</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>142</v>
+        <v>287</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4263,33 +4218,33 @@
         <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>77</v>
+        <v>224</v>
       </c>
       <c r="K53" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>286</v>
+        <v>63</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4298,33 +4253,33 @@
         <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>87</v>
+        <v>240</v>
       </c>
       <c r="K54" s="3">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>65</v>
+        <v>295</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4336,30 +4291,30 @@
         <v>288</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>56</v>
+        <v>250</v>
       </c>
       <c r="K55" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>185</v>
+        <v>297</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>142</v>
+        <v>298</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4368,33 +4323,33 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>205</v>
+        <v>68</v>
       </c>
       <c r="K56" s="3">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
@@ -4403,33 +4358,33 @@
         <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>243</v>
+        <v>129</v>
       </c>
       <c r="K57" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>298</v>
+        <v>63</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>248</v>
+        <v>65</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
@@ -4438,33 +4393,33 @@
         <v>6</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>68</v>
+        <v>306</v>
       </c>
       <c r="K58" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
@@ -4473,255 +4428,255 @@
         <v>6</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>305</v>
+        <v>202</v>
       </c>
       <c r="K59" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>65</v>
+        <v>313</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E60" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>277</v>
+        <v>314</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>309</v>
+        <v>235</v>
       </c>
       <c r="K60" s="3">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>153</v>
+        <v>316</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E61" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>255</v>
+        <v>102</v>
       </c>
       <c r="K61" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>315</v>
+        <v>91</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E62" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>273</v>
+        <v>322</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>62</v>
+        <v>324</v>
       </c>
       <c r="K62" s="3">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>185</v>
+        <v>311</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>318</v>
+        <v>71</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E63" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>104</v>
+        <v>202</v>
       </c>
       <c r="K63" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>321</v>
+        <v>45</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E64" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>326</v>
+        <v>185</v>
       </c>
       <c r="K64" s="3">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E65" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="K65" s="3">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>331</v>
+        <v>270</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>332</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>147</v>
+        <v>333</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E66" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>32</v>
@@ -4730,33 +4685,33 @@
         <v>334</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>335</v>
+        <v>169</v>
       </c>
       <c r="K66" s="3">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>336</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>65</v>
+        <v>333</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E67" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>32</v>
@@ -4765,7 +4720,7 @@
         <v>337</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>104</v>
+        <v>250</v>
       </c>
       <c r="K67" s="3">
         <v>0</v>
@@ -4773,13 +4728,13 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>45</v>
+        <v>338</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>323</v>
+        <v>91</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>25</v>
@@ -4788,335 +4743,92 @@
         <v>3</v>
       </c>
       <c r="F68" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J68" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="G68" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="K68" s="3">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>147</v>
+        <v>344</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E69" s="3">
-        <v>3</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>341</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>56</v>
+        <v>202</v>
       </c>
       <c r="K69" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>344</v>
+        <v>181</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E70" s="3">
-        <v>3</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>324</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="K70" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E71" s="3">
-        <v>3</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="K71" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E72" s="3">
-        <v>3</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K72" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E73" s="3">
-        <v>3</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="K73" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E74" s="3">
-        <v>3</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K74" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="D75" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E75" s="3">
-        <v>0</v>
-      </c>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="J75" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="K75" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E76" s="3">
-        <v>0</v>
-      </c>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K76" s="3">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E77" s="3">
-        <v>0</v>
-      </c>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K77" s="3">
-        <v>25</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K77"/>
+  <autoFilter ref="A1:K70"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5187,13 +4899,6 @@
     <hyperlink ref="I68" r:id="rId67"/>
     <hyperlink ref="I69" r:id="rId68"/>
     <hyperlink ref="I70" r:id="rId69"/>
-    <hyperlink ref="I71" r:id="rId70"/>
-    <hyperlink ref="I72" r:id="rId71"/>
-    <hyperlink ref="I73" r:id="rId72"/>
-    <hyperlink ref="I74" r:id="rId73"/>
-    <hyperlink ref="I75" r:id="rId74"/>
-    <hyperlink ref="I76" r:id="rId75"/>
-    <hyperlink ref="I77" r:id="rId76"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5201,11 +4906,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="52" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="48" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -5224,10 +4929,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -5235,221 +4940,79 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>99</v>
+        <v>245</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>100</v>
+        <v>246</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>102</v>
+        <v>248</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>103</v>
+        <v>249</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>104</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>118</v>
+        <v>293</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>119</v>
+        <v>294</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>120</v>
+        <v>288</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>121</v>
+        <v>296</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>104</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>215</v>
+        <v>335</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>216</v>
+        <v>336</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>217</v>
+        <v>322</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>218</v>
+        <v>337</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3">
-        <v>13</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="3">
-        <v>10</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="3">
-        <v>10</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3">
-        <v>6</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="3">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="3">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>104</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G4"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
-    <hyperlink ref="F9" r:id="rId8"/>
-    <hyperlink ref="F10" r:id="rId9"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5464,178 +5027,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="B2" s="3">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="B3" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="B6" s="3">
         <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>373</v>
+        <v>318</v>
       </c>
       <c r="B7" s="3">
         <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>377</v>
+        <v>340</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="B14" s="3">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -5655,10 +5218,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
@@ -5666,10 +5229,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3">
@@ -5677,10 +5240,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4">
@@ -5688,10 +5251,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5">
@@ -5702,7 +5265,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6">
@@ -5710,10 +5273,10 @@
         <v>29</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7">
@@ -5724,7 +5287,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -5745,13 +5308,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>401</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
@@ -5762,7 +5325,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5771,10 +5334,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -5786,7 +5349,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="D4" s="3"/>
     </row>
